--- a/reports/virginatlantic-where-we-fly-blocks.xlsx
+++ b/reports/virginatlantic-where-we-fly-blocks.xlsx
@@ -11,27 +11,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="73">
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>Base block</t>
-  </si>
-  <si>
-    <t>Variant ID</t>
-  </si>
-  <si>
-    <t>Description</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="100">
+  <si>
+    <t>Include</t>
+  </si>
+  <si>
+    <t>Row type</t>
+  </si>
+  <si>
+    <t>Block name</t>
+  </si>
+  <si>
+    <t>Internal ID</t>
+  </si>
+  <si>
+    <t>Variations</t>
   </si>
   <si>
     <t>Build complexity</t>
   </si>
   <si>
-    <t>EDS mapping</t>
-  </si>
-  <si>
-    <t>Pages</t>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Core block type</t>
+  </si>
+  <si>
+    <t>Tags</t>
+  </si>
+  <si>
+    <t>Notes</t>
   </si>
   <si>
     <t>Screenshot</t>
@@ -40,28 +49,124 @@
     <t>Source URL</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Main block</t>
+  </si>
+  <si>
+    <t>Header / Footer</t>
+  </si>
+  <si>
+    <t>BLK-HEADER-FOOTER</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Core</t>
+  </si>
+  <si>
+    <t>header-footer, core</t>
+  </si>
+  <si>
+    <t>2 variants · 264 instances in section</t>
+  </si>
+  <si>
+    <t>https://www.virginatlantic.com/en-IN/where-we-fly</t>
+  </si>
+  <si>
+    <t>↳ Variation</t>
+  </si>
+  <si>
+    <t>footer-global</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Block variant: footer · 132 pages</t>
+  </si>
+  <si>
+    <t>header-global</t>
+  </si>
+  <si>
+    <t>Block variant: header · 132 pages</t>
+  </si>
+  <si>
+    <t>Hero</t>
+  </si>
+  <si>
+    <t>BLK-HERO</t>
+  </si>
+  <si>
+    <t>hero, core</t>
+  </si>
+  <si>
+    <t>4 variants · 528 instances in section</t>
+  </si>
+  <si>
+    <t>https://www.virginatlantic.com/en-IN/corporate/affiliates-to-india</t>
+  </si>
+  <si>
+    <t>hero-minimal-dark-withimg</t>
+  </si>
+  <si>
+    <t>heading + text + 2 images · 132 pages</t>
+  </si>
+  <si>
+    <t>hero-minimal-dark-withimg-1</t>
+  </si>
+  <si>
+    <t>heading + 2 images · 132 pages</t>
+  </si>
+  <si>
+    <t>https://www.virginatlantic.com/en-IN/experience/inflight-entertainment/connectivity/a330-300</t>
+  </si>
+  <si>
+    <t>hero-minimal-light</t>
+  </si>
+  <si>
+    <t>heading + text + 3 CTAs + list · 132 pages</t>
+  </si>
+  <si>
+    <t>https://www.virginatlantic.com/en-IN/manage-booking</t>
+  </si>
+  <si>
+    <t>hero-minimal-light-withimg</t>
+  </si>
+  <si>
+    <t>heading + text + 1 CTAs + 2 images · 132 pages</t>
+  </si>
+  <si>
+    <t>https://www.virginatlantic.com/en-IN/travel-news/changes-to-uk-entry-requirements</t>
+  </si>
+  <si>
     <t>Breadcrumbs</t>
   </si>
   <si>
+    <t>BLK-BREADCRUMBS</t>
+  </si>
+  <si>
+    <t>Simple</t>
+  </si>
+  <si>
+    <t>breadcrumbs, core</t>
+  </si>
+  <si>
+    <t>5 variants · 660 instances in section</t>
+  </si>
+  <si>
     <t>breadcrumbs-minimal-dark</t>
   </si>
   <si>
-    <t>2 CTAs + list</t>
-  </si>
-  <si>
-    <t>Simple</t>
-  </si>
-  <si>
-    <t>Standard</t>
-  </si>
-  <si>
-    <t>https://www.virginatlantic.com/en-IN/corporate/affiliates-to-india</t>
+    <t>2 CTAs + list · 132 pages</t>
   </si>
   <si>
     <t>breadcrumbs-minimal-dark-1</t>
   </si>
   <si>
-    <t>3 CTAs + list</t>
+    <t>3 CTAs + list · 132 pages</t>
   </si>
   <si>
     <t>https://www.virginatlantic.com/en-IN/corporate/business-for-good/resources</t>
@@ -70,7 +175,7 @@
     <t>breadcrumbs-minimal-light-withimg</t>
   </si>
   <si>
-    <t>heading + text + 3 CTAs + 2 images + list</t>
+    <t>heading + text + 3 CTAs + 2 images + list · 132 pages</t>
   </si>
   <si>
     <t>https://www.virginatlantic.com/en-IN/corporate/business-for-good/virgin-atlantic-foundation</t>
@@ -79,16 +184,13 @@
     <t>breadcrumbs-minimal-dark-2</t>
   </si>
   <si>
-    <t>4 CTAs + list</t>
-  </si>
-  <si>
-    <t>https://www.virginatlantic.com/en-IN/experience/inflight-entertainment/connectivity/a330-300</t>
+    <t>4 CTAs + list · 132 pages</t>
   </si>
   <si>
     <t>breadcrumbs-minimal-light-withimg-1</t>
   </si>
   <si>
-    <t>heading + text + 2 CTAs + 2 images + list</t>
+    <t>heading + text + 2 CTAs + 2 images + list · 132 pages</t>
   </si>
   <si>
     <t>https://www.virginatlantic.com/en-IN/policies/virgin-atlantic-account-terms-and-conditions</t>
@@ -97,19 +199,25 @@
     <t>Cards</t>
   </si>
   <si>
+    <t>BLK-CARDS</t>
+  </si>
+  <si>
+    <t>cards, core</t>
+  </si>
+  <si>
+    <t>3 variants · 113 instances in section</t>
+  </si>
+  <si>
     <t>cards-minimal-dark-withimg</t>
   </si>
   <si>
-    <t>heading + text + 1 CTAs + image</t>
-  </si>
-  <si>
-    <t>https://www.virginatlantic.com/en-IN/where-we-fly</t>
+    <t>heading + text + 1 CTAs + image · 107 pages</t>
   </si>
   <si>
     <t>cards-minimal-dark-withimg-1</t>
   </si>
   <si>
-    <t>heading + image</t>
+    <t>heading + image · 5 pages</t>
   </si>
   <si>
     <t>https://www.virginatlantic.com/en-IN/where-we-fly/middle-east/saudi-arabia/riyadh-airport-guide</t>
@@ -118,125 +226,98 @@
     <t>cards-minimal-dark-withimg-2</t>
   </si>
   <si>
-    <t>heading + text + image + list</t>
+    <t>heading + text + image + list · 1 page</t>
   </si>
   <si>
     <t>https://www.virginatlantic.com/en-IN/where-we-fly/north-america/usa/california/perfect-5-day-itinerary</t>
   </si>
   <si>
+    <t>Table</t>
+  </si>
+  <si>
+    <t>BLK-TABLE</t>
+  </si>
+  <si>
+    <t>table, core</t>
+  </si>
+  <si>
+    <t>1 variant · 1 instances in section</t>
+  </si>
+  <si>
+    <t>https://www.virginatlantic.com/en-IN/where-we-fly/caribbean/tobago</t>
+  </si>
+  <si>
+    <t>table-minimal-dark</t>
+  </si>
+  <si>
+    <t>heading + text + image · 1 page</t>
+  </si>
+  <si>
     <t>Form</t>
   </si>
   <si>
+    <t>BLK-FORM</t>
+  </si>
+  <si>
+    <t>form, core</t>
+  </si>
+  <si>
     <t>form-minimal-dark</t>
   </si>
   <si>
-    <t>9 CTAs</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>https://www.virginatlantic.com/en-IN/where-we-fly/caribbean/tobago</t>
-  </si>
-  <si>
-    <t>Hero</t>
-  </si>
-  <si>
-    <t>hero-minimal-dark-withimg</t>
-  </si>
-  <si>
-    <t>heading + text + 2 images</t>
-  </si>
-  <si>
-    <t>hero-minimal-dark-withimg-1</t>
-  </si>
-  <si>
-    <t>heading + 2 images</t>
-  </si>
-  <si>
-    <t>hero-minimal-light</t>
-  </si>
-  <si>
-    <t>heading + text + 3 CTAs + list</t>
-  </si>
-  <si>
-    <t>https://www.virginatlantic.com/en-IN/manage-booking</t>
-  </si>
-  <si>
-    <t>hero-minimal-light-withimg</t>
-  </si>
-  <si>
-    <t>heading + text + 1 CTAs + 2 images</t>
-  </si>
-  <si>
-    <t>https://www.virginatlantic.com/en-IN/travel-news/changes-to-uk-entry-requirements</t>
-  </si>
-  <si>
-    <t>Header / Footer</t>
-  </si>
-  <si>
-    <t>footer-global</t>
-  </si>
-  <si>
-    <t>Block variant: footer</t>
-  </si>
-  <si>
-    <t>header-global</t>
-  </si>
-  <si>
-    <t>Block variant: header</t>
-  </si>
-  <si>
-    <t>Table</t>
-  </si>
-  <si>
-    <t>table-minimal-dark</t>
-  </si>
-  <si>
-    <t>heading + text + image</t>
+    <t>9 CTAs · 1 page</t>
   </si>
   <si>
     <t>Unknown / Custom</t>
   </si>
   <si>
+    <t>BLK-UNKNOWN-CUSTOM</t>
+  </si>
+  <si>
+    <t>Complex</t>
+  </si>
+  <si>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t>unknown-custom, custom</t>
+  </si>
+  <si>
+    <t>4 variants · 6 instances in section</t>
+  </si>
+  <si>
+    <t>https://www.virginatlantic.com/en-IN/where-we-fly/africa/south-africa</t>
+  </si>
+  <si>
     <t>1 heading block-minimal-dark</t>
   </si>
   <si>
-    <t>heading</t>
-  </si>
-  <si>
-    <t>Complex</t>
-  </si>
-  <si>
-    <t>Custom</t>
-  </si>
-  <si>
-    <t>https://www.virginatlantic.com/en-IN/where-we-fly/africa/south-africa</t>
+    <t>heading · 3 pages</t>
   </si>
   <si>
     <t>1 image block-minimal-dark-withimg</t>
   </si>
   <si>
-    <t>image</t>
+    <t>image · 1 page</t>
   </si>
   <si>
     <t>1 heading + 1 cta + 1 list block-minimal-dark</t>
   </si>
   <si>
-    <t>heading + 1 CTAs + list</t>
+    <t>heading + 1 CTAs + list · 1 page</t>
   </si>
   <si>
     <t>7 images block-minimal-dark</t>
   </si>
   <si>
-    <t>text + 7 images</t>
+    <t>text + 7 images · 1 page</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -251,22 +332,28 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF1C7A3E"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFA9701A"/>
     </font>
     <font>
       <u/>
       <color rgb="FF0563C1"/>
     </font>
     <font>
+      <i/>
+    </font>
+    <font>
       <b/>
-      <color rgb="FFA9701A"/>
+      <color rgb="FF1C7A3E"/>
     </font>
     <font>
       <b/>
       <color rgb="FFC0140A"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -280,12 +367,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE3F5E8"/>
+        <fgColor rgb="FFF4F2F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFBEFDC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F5E8"/>
       </patternFill>
     </fill>
     <fill>
@@ -306,30 +398,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -353,12 +451,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>45999</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>18000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2857500" cy="180975"/>
+    <xdr:ext cx="1790700" cy="1428750"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">
@@ -392,12 +490,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>45999</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>18000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2857500" cy="180975"/>
+    <xdr:ext cx="1790700" cy="1428750"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 2">
@@ -431,12 +529,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>45999</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>18000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2857500" cy="1409700"/>
+    <xdr:ext cx="2857500" cy="161925"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Picture 3">
@@ -470,12 +568,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>45999</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>17999</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2857500" cy="180975"/>
+    <xdr:ext cx="2857500" cy="847725"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="4" name="Picture 4">
@@ -509,12 +607,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>45999</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>17999</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2857500" cy="1352550"/>
+    <xdr:ext cx="2857500" cy="847725"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="5" name="Picture 5">
@@ -548,12 +646,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>45999</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>17999</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1104900" cy="1428750"/>
+    <xdr:ext cx="2857500" cy="638175"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="6" name="Picture 6">
@@ -587,12 +685,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>45999</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>17999</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1971675" cy="1428750"/>
+    <xdr:ext cx="2857500" cy="1266825"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="7" name="Picture 7">
@@ -626,12 +724,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>45999</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>17999</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2857500" cy="819150"/>
+    <xdr:ext cx="2314575" cy="1428750"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="8" name="Picture 8">
@@ -665,12 +763,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>45999</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>17999</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2552700" cy="1428750"/>
+    <xdr:ext cx="2857500" cy="180975"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="9" name="Picture 9">
@@ -704,12 +802,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>45999</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>17999</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2857500" cy="847725"/>
+    <xdr:ext cx="2857500" cy="180975"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="10" name="Picture 10">
@@ -743,12 +841,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>45999</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>17999</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2857500" cy="638175"/>
+    <xdr:ext cx="2857500" cy="180975"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="11" name="Picture 11">
@@ -782,12 +880,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>45999</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>17999</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2857500" cy="1266825"/>
+    <xdr:ext cx="2857500" cy="1409700"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="12" name="Picture 12">
@@ -821,12 +919,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>45999</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>17999</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2314575" cy="1428750"/>
+    <xdr:ext cx="2857500" cy="180975"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="13" name="Picture 13">
@@ -860,12 +958,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>45999</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>17999</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1790700" cy="1428750"/>
+    <xdr:ext cx="2857500" cy="1352550"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="14" name="Picture 14">
@@ -899,12 +997,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>45999</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>17999</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2857500" cy="161925"/>
+    <xdr:ext cx="1104900" cy="1428750"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="15" name="Picture 15">
@@ -938,12 +1036,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>45999</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>18000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2857500" cy="428625"/>
+    <xdr:ext cx="1104900" cy="1428750"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="16" name="Picture 16">
@@ -977,12 +1075,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>45999</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>18000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2857500" cy="428625"/>
+    <xdr:ext cx="1971675" cy="1428750"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="17" name="Picture 17">
@@ -1016,12 +1114,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>45999</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>18000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2857500" cy="1123950"/>
+    <xdr:ext cx="2857500" cy="819150"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="18" name="Picture 18">
@@ -1055,12 +1153,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>45999</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>18000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2857500" cy="447675"/>
+    <xdr:ext cx="2857500" cy="428625"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="19" name="Picture 19">
@@ -1094,12 +1192,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>45999</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>18000</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2857500" cy="666750"/>
+    <xdr:ext cx="2857500" cy="428625"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="20" name="Picture 20">
@@ -1115,6 +1213,279 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>45999</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>18000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2552700" cy="1428750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="Picture 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>45999</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>18000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2552700" cy="1428750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="Picture 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>45999</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>18000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2857500" cy="428625"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="Picture 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>45999</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>18000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2857500" cy="428625"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="Picture 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>45999</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>18000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2857500" cy="1123950"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="Picture 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>45999</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>18000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2857500" cy="447675"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="Picture 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>45999</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>18000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2857500" cy="666750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="Picture 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1456,21 +1827,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="34" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="46" customWidth="1"/>
-    <col min="9" max="9" width="70" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="10" max="10" width="40" customWidth="1"/>
+    <col min="11" max="11" width="46" customWidth="1"/>
+    <col min="12" max="12" width="66" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1498,553 +1871,994 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" ht="40" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" ht="125" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="4">
+        <v>2</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" ht="125" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" ht="77.42" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="4">
+        <v>4</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" ht="77.42" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" ht="60.260000000000005" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" ht="111.74000000000001" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" ht="125" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="4">
+        <v>5</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" ht="123.44" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" ht="118.76" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" ht="125" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="4">
+        <v>3</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" ht="125" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" ht="125" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" t="s">
+        <v>23</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" ht="75.08" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" t="s">
+        <v>23</v>
+      </c>
+      <c r="I19" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" ht="43.1" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="F20" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" ht="43.1" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B21" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" t="s">
+        <v>23</v>
+      </c>
+      <c r="I21" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" ht="125" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="5">
-        <v>132</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>14</v>
+      <c r="C22" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E22" s="4">
+        <v>1</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="3" ht="40" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="3" t="s">
+    <row r="23" ht="125" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="G23" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" t="s">
+        <v>23</v>
+      </c>
+      <c r="I23" t="s">
+        <v>23</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" ht="43.1" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F3" t="s">
+      <c r="B24" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="5">
-        <v>132</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>17</v>
+      <c r="C24" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" s="4">
+        <v>4</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>91</v>
       </c>
     </row>
-    <row r="4" ht="123.44" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="4" t="s">
+    <row r="25" ht="43.1" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="5">
-        <v>132</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>20</v>
+      <c r="B25" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H25" t="s">
+        <v>23</v>
+      </c>
+      <c r="I25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>91</v>
       </c>
     </row>
-    <row r="5" ht="40" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="3" t="s">
+    <row r="26" ht="100.04" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="C26" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" t="s">
+        <v>23</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H26" t="s">
+        <v>23</v>
+      </c>
+      <c r="I26" t="s">
+        <v>23</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" ht="44.660000000000004" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="5">
-        <v>132</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>23</v>
+      <c r="B27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" t="s">
+        <v>23</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H27" t="s">
+        <v>23</v>
+      </c>
+      <c r="I27" t="s">
+        <v>23</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="6" ht="118.76" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="4" t="s">
+    <row r="28" ht="62.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="5">
-        <v>132</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" ht="125" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="5">
-        <v>107</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" ht="125" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="5">
-        <v>5</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" ht="75.08" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="5">
-        <v>1</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" ht="125" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="5">
-        <v>1</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" ht="77.42" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="5">
-        <v>132</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" ht="60.260000000000005" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="5">
-        <v>132</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" ht="111.74000000000001" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="5">
-        <v>132</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" ht="125" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="5">
-        <v>132</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" ht="125" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="5">
-        <v>132</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" ht="40" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="5">
-        <v>132</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" ht="43.1" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="5">
-        <v>1</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" ht="43.1" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F18" t="s">
-        <v>65</v>
-      </c>
-      <c r="G18" s="5">
-        <v>3</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" ht="100.04" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F19" t="s">
-        <v>65</v>
-      </c>
-      <c r="G19" s="5">
-        <v>1</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" ht="44.660000000000004" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F20" t="s">
-        <v>65</v>
-      </c>
-      <c r="G20" s="5">
-        <v>1</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" ht="62.6" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F21" t="s">
-        <v>65</v>
-      </c>
-      <c r="G21" s="5">
-        <v>1</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>41</v>
+      <c r="B28" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D28" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H28" t="s">
+        <v>23</v>
+      </c>
+      <c r="I28" t="s">
+        <v>23</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:L1"/>
   <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1"/>
-    <hyperlink ref="I3" r:id="rId2"/>
-    <hyperlink ref="I4" r:id="rId3"/>
-    <hyperlink ref="I5" r:id="rId4"/>
-    <hyperlink ref="I6" r:id="rId5"/>
-    <hyperlink ref="I7" r:id="rId6"/>
-    <hyperlink ref="I8" r:id="rId7"/>
-    <hyperlink ref="I9" r:id="rId8"/>
-    <hyperlink ref="I10" r:id="rId9"/>
-    <hyperlink ref="I11" r:id="rId10"/>
-    <hyperlink ref="I12" r:id="rId11"/>
-    <hyperlink ref="I13" r:id="rId12"/>
-    <hyperlink ref="I14" r:id="rId13"/>
-    <hyperlink ref="I15" r:id="rId14"/>
-    <hyperlink ref="I16" r:id="rId15"/>
-    <hyperlink ref="I17" r:id="rId16"/>
-    <hyperlink ref="I18" r:id="rId17"/>
-    <hyperlink ref="I19" r:id="rId18"/>
-    <hyperlink ref="I20" r:id="rId19"/>
-    <hyperlink ref="I21" r:id="rId20"/>
+    <hyperlink ref="L2" r:id="rId1"/>
+    <hyperlink ref="L3" r:id="rId2"/>
+    <hyperlink ref="L4" r:id="rId3"/>
+    <hyperlink ref="L5" r:id="rId4"/>
+    <hyperlink ref="L6" r:id="rId5"/>
+    <hyperlink ref="L7" r:id="rId6"/>
+    <hyperlink ref="L8" r:id="rId7"/>
+    <hyperlink ref="L9" r:id="rId8"/>
+    <hyperlink ref="L10" r:id="rId9"/>
+    <hyperlink ref="L11" r:id="rId10"/>
+    <hyperlink ref="L12" r:id="rId11"/>
+    <hyperlink ref="L13" r:id="rId12"/>
+    <hyperlink ref="L14" r:id="rId13"/>
+    <hyperlink ref="L15" r:id="rId14"/>
+    <hyperlink ref="L16" r:id="rId15"/>
+    <hyperlink ref="L17" r:id="rId16"/>
+    <hyperlink ref="L18" r:id="rId17"/>
+    <hyperlink ref="L19" r:id="rId18"/>
+    <hyperlink ref="L20" r:id="rId19"/>
+    <hyperlink ref="L21" r:id="rId20"/>
+    <hyperlink ref="L22" r:id="rId21"/>
+    <hyperlink ref="L23" r:id="rId22"/>
+    <hyperlink ref="L24" r:id="rId23"/>
+    <hyperlink ref="L25" r:id="rId24"/>
+    <hyperlink ref="L26" r:id="rId25"/>
+    <hyperlink ref="L27" r:id="rId26"/>
+    <hyperlink ref="L28" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <drawing r:id="rId21"/>
+  <drawing r:id="rId28"/>
 </worksheet>
 </file>